--- a/JAM01N.xlsx
+++ b/JAM01N.xlsx
@@ -223,7 +223,7 @@
     <t>10036685</t>
   </si>
   <si>
-    <t>NUTELLA JAM HZLNT200</t>
+    <t>NUTELLA J HZNT 200 G</t>
   </si>
   <si>
     <t>20137767</t>
